--- a/fixtures/jeju/timetables/bis/raw/406056.xlsx
+++ b/fixtures/jeju/timetables/bis/raw/406056.xlsx
@@ -6,8 +6,8 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="500 모슬포남항-화순-중문-월드컵경기장-중앙R-" r:id="rId3" sheetId="1"/>
-    <sheet name="500 남원환승-중앙R-월드컵경기장-중문-화순-모" r:id="rId4" sheetId="2"/>
+    <sheet name="500 남원환승-중앙R-월드컵경기장-중문-화순-모" r:id="rId3" sheetId="1"/>
+    <sheet name="500 모슬포남항-화순-중문-월드컵경기장-중앙R-" r:id="rId4" sheetId="2"/>
   </sheets>
 </workbook>
 </file>
@@ -18,32 +18,373 @@
     <t>구분</t>
   </si>
   <si>
+    <t>남원환승정류장</t>
+  </si>
+  <si>
+    <t>서귀포환승정류장
+(서귀포등기소)</t>
+  </si>
+  <si>
+    <t>제주월드컵경기장
+서귀포버스터미널</t>
+  </si>
+  <si>
+    <t>중문환승정류장
+중문우체국</t>
+  </si>
+  <si>
+    <t>화순환승정류장
+안덕농협</t>
+  </si>
+  <si>
     <t>모슬포남항 
 (운진항)</t>
   </si>
   <si>
-    <t>화순환승정류장
-안덕농협</t>
-  </si>
-  <si>
-    <t>중문환승정류장
-중문우체국</t>
-  </si>
-  <si>
-    <t>제주월드컵경기장
-서귀포버스터미널</t>
+    <t>x</t>
+  </si>
+  <si>
+    <t>5:50
+(출발)</t>
+  </si>
+  <si>
+    <t>06:00</t>
+  </si>
+  <si>
+    <t>06:14</t>
+  </si>
+  <si>
+    <t>06:30</t>
+  </si>
+  <si>
+    <t>06:51</t>
+  </si>
+  <si>
+    <t>6:30
+(출발)</t>
+  </si>
+  <si>
+    <t>06:40</t>
+  </si>
+  <si>
+    <t>06:54</t>
+  </si>
+  <si>
+    <t>07:10</t>
+  </si>
+  <si>
+    <t>07:31</t>
+  </si>
+  <si>
+    <t>06:35</t>
+  </si>
+  <si>
+    <t>07:07</t>
+  </si>
+  <si>
+    <t>07:17</t>
+  </si>
+  <si>
+    <t>07:33</t>
+  </si>
+  <si>
+    <t>07:53</t>
+  </si>
+  <si>
+    <t>08:14</t>
+  </si>
+  <si>
+    <t>07:05</t>
+  </si>
+  <si>
+    <t>07:37</t>
+  </si>
+  <si>
+    <t>07:47</t>
+  </si>
+  <si>
+    <t>08:03</t>
+  </si>
+  <si>
+    <t>08:23</t>
+  </si>
+  <si>
+    <t>08:44</t>
+  </si>
+  <si>
+    <t>08:10</t>
+  </si>
+  <si>
+    <t>08:42</t>
+  </si>
+  <si>
+    <t>08:52</t>
+  </si>
+  <si>
+    <t>09:08</t>
+  </si>
+  <si>
+    <t>09:28</t>
+  </si>
+  <si>
+    <t>09:49</t>
+  </si>
+  <si>
+    <t>09:10</t>
+  </si>
+  <si>
+    <t>09:42</t>
+  </si>
+  <si>
+    <t>09:52</t>
+  </si>
+  <si>
+    <t>10:08</t>
+  </si>
+  <si>
+    <t>10:28</t>
+  </si>
+  <si>
+    <t>10:49</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>10:32</t>
+  </si>
+  <si>
+    <t>10:42</t>
+  </si>
+  <si>
+    <t>10:58</t>
+  </si>
+  <si>
+    <t>11:18</t>
+  </si>
+  <si>
+    <t>11:39</t>
+  </si>
+  <si>
+    <t>10:50</t>
+  </si>
+  <si>
+    <t>11:22</t>
+  </si>
+  <si>
+    <t>11:32</t>
+  </si>
+  <si>
+    <t>11:48</t>
+  </si>
+  <si>
+    <t>12:08</t>
+  </si>
+  <si>
+    <t>12:29</t>
+  </si>
+  <si>
+    <t>11:50</t>
+  </si>
+  <si>
+    <t>12:22</t>
+  </si>
+  <si>
+    <t>12:32</t>
+  </si>
+  <si>
+    <t>12:48</t>
+  </si>
+  <si>
+    <t>13:08</t>
+  </si>
+  <si>
+    <t>13:29</t>
+  </si>
+  <si>
+    <t>12:50</t>
+  </si>
+  <si>
+    <t>13:22</t>
+  </si>
+  <si>
+    <t>13:32</t>
+  </si>
+  <si>
+    <t>13:48</t>
+  </si>
+  <si>
+    <t>14:08</t>
+  </si>
+  <si>
+    <t>14:29</t>
+  </si>
+  <si>
+    <t>13:50</t>
+  </si>
+  <si>
+    <t>14:22</t>
+  </si>
+  <si>
+    <t>14:32</t>
+  </si>
+  <si>
+    <t>14:48</t>
+  </si>
+  <si>
+    <t>15:08</t>
+  </si>
+  <si>
+    <t>15:29</t>
+  </si>
+  <si>
+    <t>14:50</t>
+  </si>
+  <si>
+    <t>15:22</t>
+  </si>
+  <si>
+    <t>15:32</t>
+  </si>
+  <si>
+    <t>15:48</t>
+  </si>
+  <si>
+    <t>16:08</t>
+  </si>
+  <si>
+    <t>16:29</t>
+  </si>
+  <si>
+    <t>15:50</t>
+  </si>
+  <si>
+    <t>16:24</t>
+  </si>
+  <si>
+    <t>16:34</t>
+  </si>
+  <si>
+    <t>16:50</t>
+  </si>
+  <si>
+    <t>17:10</t>
+  </si>
+  <si>
+    <t>17:31</t>
+  </si>
+  <si>
+    <t>16:40</t>
+  </si>
+  <si>
+    <t>17:14</t>
+  </si>
+  <si>
+    <t>17:24</t>
+  </si>
+  <si>
+    <t>17:40</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>18:21</t>
+  </si>
+  <si>
+    <t>17:20</t>
+  </si>
+  <si>
+    <t>17:54</t>
+  </si>
+  <si>
+    <t>18:04</t>
+  </si>
+  <si>
+    <t>18:20</t>
+  </si>
+  <si>
+    <t>18:40</t>
+  </si>
+  <si>
+    <t>19:01</t>
+  </si>
+  <si>
+    <t>18:34</t>
+  </si>
+  <si>
+    <t>18:44</t>
+  </si>
+  <si>
+    <t>19:00</t>
+  </si>
+  <si>
+    <t>19:20</t>
+  </si>
+  <si>
+    <t>19:41</t>
+  </si>
+  <si>
+    <t>19:14</t>
+  </si>
+  <si>
+    <t>19:24</t>
+  </si>
+  <si>
+    <t>19:40</t>
+  </si>
+  <si>
+    <t>20:00</t>
+  </si>
+  <si>
+    <t>20:21</t>
+  </si>
+  <si>
+    <t>19:52</t>
+  </si>
+  <si>
+    <t>20:02</t>
+  </si>
+  <si>
+    <t>20:18</t>
+  </si>
+  <si>
+    <t>20:38</t>
+  </si>
+  <si>
+    <t>20:59</t>
+  </si>
+  <si>
+    <t>20:32
+(종료)</t>
+  </si>
+  <si>
+    <t>20:40</t>
+  </si>
+  <si>
+    <t>21:12
+(종료)</t>
+  </si>
+  <si>
+    <t>500번(도심급행)</t>
+  </si>
+  <si>
+    <t>[500번]남원환승정류장(남원읍사무소)-위미2리 교차로-공천포-효돈농협하나로마트-삼성여자고등학교-국민연금공단서귀포지사-동흥사거리-서귀포환승정류장(서귀포등기소)-서귀포여자중학교-제주월드컵경기장 서귀포버스터미널-하원동-중문고등학교-중문환승정류장(중문우체국)-중문관광단지입구-예래입구-창천초등학교-화순환승정류장(안덕농협)-인성리(남문지앞사거리)-대정고등학교-하모3리 축협-하모체육공원-모슬포 남항 여객선 터미널(운진항)</t>
+  </si>
+  <si>
+    <t>남원→ 일주도로→ 모슬포남항(운진항)</t>
+  </si>
+  <si>
+    <t>첫차(서귀포등기소 출발) 5:50, 막차 21:40, 배차간격 40분~60분, 서귀포운수(064-732-4934)</t>
+  </si>
+  <si>
+    <t>(시행일 : 2026.3.3.)</t>
   </si>
   <si>
     <t>서귀포중앙로터리
 (권역재활병원)</t>
   </si>
   <si>
-    <t>남원환승정류장</t>
-  </si>
-  <si>
-    <t>x</t>
-  </si>
-  <si>
     <t>6:25
 (출발)</t>
   </si>
@@ -58,21 +399,12 @@
     <t>07:30</t>
   </si>
   <si>
-    <t>06:30</t>
-  </si>
-  <si>
-    <t>06:51</t>
-  </si>
-  <si>
     <t>07:11</t>
   </si>
   <si>
     <t>07:27</t>
   </si>
   <si>
-    <t>07:37</t>
-  </si>
-  <si>
     <t>08:07</t>
   </si>
   <si>
@@ -91,9 +423,6 @@
     <t>08:22</t>
   </si>
   <si>
-    <t>08:52</t>
-  </si>
-  <si>
     <t>08:00</t>
   </si>
   <si>
@@ -130,9 +459,6 @@
     <t>10:27</t>
   </si>
   <si>
-    <t>10:00</t>
-  </si>
-  <si>
     <t>10:21</t>
   </si>
   <si>
@@ -148,9 +474,6 @@
     <t>11:37</t>
   </si>
   <si>
-    <t>10:50</t>
-  </si>
-  <si>
     <t>11:11</t>
   </si>
   <si>
@@ -166,9 +489,6 @@
     <t>12:27</t>
   </si>
   <si>
-    <t>11:50</t>
-  </si>
-  <si>
     <t>12:11</t>
   </si>
   <si>
@@ -289,12 +609,6 @@
     <t>18:37</t>
   </si>
   <si>
-    <t>18:00</t>
-  </si>
-  <si>
-    <t>18:21</t>
-  </si>
-  <si>
     <t>18:41</t>
   </si>
   <si>
@@ -325,13 +639,7 @@
     <t>20:27</t>
   </si>
   <si>
-    <t>19:40</t>
-  </si>
-  <si>
     <t>20:01</t>
-  </si>
-  <si>
-    <t>20:21</t>
   </si>
   <si>
     <t>20:37</t>
@@ -372,9 +680,6 @@
 (종료)</t>
   </si>
   <si>
-    <t>500번(도심급행)</t>
-  </si>
-  <si>
     <t>[500번]모슬포 남항 여객선 터미널(운진항)-하모체육공원-대정환승정류장(대정읍사무소-해병부대-인성리(남문지앞사거리)-화순환승정류장(안덕농협)-창천초등학교-예래입구-중문관광단지입구-중문환승정류장(중문우체국)-중문고등학교-하원동-월드컵경기장 서귀포버스터미널-서귀포여자중학교-중앙로터리/제주권역재활병원-동홍사거리-국민연금공단서귀포지사-삼성여자고등학교-효돈농협하나로마트-공천포-위미2리교차로-남원환승정류장(남원읍사무소)</t>
   </si>
   <si>
@@ -382,311 +687,6 @@
   </si>
   <si>
     <t>첫차(서귀포중앙로터리 출발) 6:25, 막차 21:00, 배차간격 30분~70분, 서귀포운수(064-732-4934)</t>
-  </si>
-  <si>
-    <t>(시행일 : 2026.3.3.)</t>
-  </si>
-  <si>
-    <t>서귀포환승정류장
-(서귀포등기소)</t>
-  </si>
-  <si>
-    <t>5:50
-(출발)</t>
-  </si>
-  <si>
-    <t>06:00</t>
-  </si>
-  <si>
-    <t>06:14</t>
-  </si>
-  <si>
-    <t>6:30
-(출발)</t>
-  </si>
-  <si>
-    <t>06:40</t>
-  </si>
-  <si>
-    <t>06:54</t>
-  </si>
-  <si>
-    <t>07:10</t>
-  </si>
-  <si>
-    <t>07:31</t>
-  </si>
-  <si>
-    <t>06:35</t>
-  </si>
-  <si>
-    <t>07:07</t>
-  </si>
-  <si>
-    <t>07:17</t>
-  </si>
-  <si>
-    <t>07:33</t>
-  </si>
-  <si>
-    <t>07:53</t>
-  </si>
-  <si>
-    <t>08:14</t>
-  </si>
-  <si>
-    <t>07:05</t>
-  </si>
-  <si>
-    <t>07:47</t>
-  </si>
-  <si>
-    <t>08:03</t>
-  </si>
-  <si>
-    <t>08:23</t>
-  </si>
-  <si>
-    <t>08:44</t>
-  </si>
-  <si>
-    <t>08:10</t>
-  </si>
-  <si>
-    <t>08:42</t>
-  </si>
-  <si>
-    <t>09:08</t>
-  </si>
-  <si>
-    <t>09:28</t>
-  </si>
-  <si>
-    <t>09:49</t>
-  </si>
-  <si>
-    <t>09:10</t>
-  </si>
-  <si>
-    <t>09:42</t>
-  </si>
-  <si>
-    <t>09:52</t>
-  </si>
-  <si>
-    <t>10:08</t>
-  </si>
-  <si>
-    <t>10:28</t>
-  </si>
-  <si>
-    <t>10:49</t>
-  </si>
-  <si>
-    <t>10:32</t>
-  </si>
-  <si>
-    <t>10:42</t>
-  </si>
-  <si>
-    <t>10:58</t>
-  </si>
-  <si>
-    <t>11:18</t>
-  </si>
-  <si>
-    <t>11:39</t>
-  </si>
-  <si>
-    <t>11:22</t>
-  </si>
-  <si>
-    <t>11:32</t>
-  </si>
-  <si>
-    <t>11:48</t>
-  </si>
-  <si>
-    <t>12:08</t>
-  </si>
-  <si>
-    <t>12:29</t>
-  </si>
-  <si>
-    <t>12:22</t>
-  </si>
-  <si>
-    <t>12:32</t>
-  </si>
-  <si>
-    <t>12:48</t>
-  </si>
-  <si>
-    <t>13:08</t>
-  </si>
-  <si>
-    <t>13:29</t>
-  </si>
-  <si>
-    <t>12:50</t>
-  </si>
-  <si>
-    <t>13:22</t>
-  </si>
-  <si>
-    <t>13:32</t>
-  </si>
-  <si>
-    <t>13:48</t>
-  </si>
-  <si>
-    <t>14:08</t>
-  </si>
-  <si>
-    <t>14:29</t>
-  </si>
-  <si>
-    <t>13:50</t>
-  </si>
-  <si>
-    <t>14:22</t>
-  </si>
-  <si>
-    <t>14:32</t>
-  </si>
-  <si>
-    <t>14:48</t>
-  </si>
-  <si>
-    <t>15:08</t>
-  </si>
-  <si>
-    <t>15:29</t>
-  </si>
-  <si>
-    <t>14:50</t>
-  </si>
-  <si>
-    <t>15:22</t>
-  </si>
-  <si>
-    <t>15:32</t>
-  </si>
-  <si>
-    <t>15:48</t>
-  </si>
-  <si>
-    <t>16:08</t>
-  </si>
-  <si>
-    <t>16:29</t>
-  </si>
-  <si>
-    <t>15:50</t>
-  </si>
-  <si>
-    <t>16:24</t>
-  </si>
-  <si>
-    <t>16:34</t>
-  </si>
-  <si>
-    <t>16:50</t>
-  </si>
-  <si>
-    <t>17:10</t>
-  </si>
-  <si>
-    <t>17:31</t>
-  </si>
-  <si>
-    <t>16:40</t>
-  </si>
-  <si>
-    <t>17:14</t>
-  </si>
-  <si>
-    <t>17:24</t>
-  </si>
-  <si>
-    <t>17:40</t>
-  </si>
-  <si>
-    <t>17:20</t>
-  </si>
-  <si>
-    <t>17:54</t>
-  </si>
-  <si>
-    <t>18:04</t>
-  </si>
-  <si>
-    <t>18:20</t>
-  </si>
-  <si>
-    <t>18:40</t>
-  </si>
-  <si>
-    <t>19:01</t>
-  </si>
-  <si>
-    <t>18:34</t>
-  </si>
-  <si>
-    <t>18:44</t>
-  </si>
-  <si>
-    <t>19:00</t>
-  </si>
-  <si>
-    <t>19:20</t>
-  </si>
-  <si>
-    <t>19:41</t>
-  </si>
-  <si>
-    <t>19:14</t>
-  </si>
-  <si>
-    <t>19:24</t>
-  </si>
-  <si>
-    <t>20:00</t>
-  </si>
-  <si>
-    <t>19:52</t>
-  </si>
-  <si>
-    <t>20:02</t>
-  </si>
-  <si>
-    <t>20:18</t>
-  </si>
-  <si>
-    <t>20:38</t>
-  </si>
-  <si>
-    <t>20:59</t>
-  </si>
-  <si>
-    <t>20:32
-(종료)</t>
-  </si>
-  <si>
-    <t>20:40</t>
-  </si>
-  <si>
-    <t>21:12
-(종료)</t>
-  </si>
-  <si>
-    <t>[500번]남원환승정류장(남원읍사무소)-위미2리 교차로-공천포-효돈농협하나로마트-삼성여자고등학교-국민연금공단서귀포지사-동흥사거리-서귀포환승정류장(서귀포등기소)-서귀포여자중학교-제주월드컵경기장 서귀포버스터미널-하원동-중문고등학교-중문환승정류장(중문우체국)-중문관광단지입구-예래입구-창천초등학교-화순환승정류장(안덕농협)-인성리(남문지앞사거리)-대정고등학교-하모3리 축협-하모체육공원-모슬포 남항 여객선 터미널(운진항)</t>
-  </si>
-  <si>
-    <t>남원→ 일주도로→ 모슬포남항(운진항)</t>
-  </si>
-  <si>
-    <t>첫차(서귀포등기소 출발) 5:50, 막차 21:40, 배차간격 40분~60분, 서귀포운수(064-732-4934)</t>
   </si>
 </sst>
 </file>
@@ -1076,20 +1076,20 @@
   <sheetData>
     <row r="2" ht="100.0" customHeight="true">
       <c r="B2" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
     </row>
     <row r="3" ht="25.0" customHeight="true">
       <c r="B3" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -1109,14 +1109,14 @@
     </row>
     <row r="5" ht="25.0" customHeight="true">
       <c r="B5" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C5"/>
       <c r="D5"/>
       <c r="E5"/>
       <c r="F5"/>
       <c r="G5" s="7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="H5"/>
     </row>
@@ -1160,19 +1160,19 @@
         <v>7</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H8" s="13" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" ht="40.0" customHeight="true">
@@ -1183,19 +1183,19 @@
         <v>7</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" ht="40.0" customHeight="true">
@@ -1203,22 +1203,22 @@
         <v>3.0</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" ht="40.0" customHeight="true">
@@ -1226,22 +1226,22 @@
         <v>4.0</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" ht="40.0" customHeight="true">
@@ -1249,22 +1249,22 @@
         <v>5.0</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" ht="40.0" customHeight="true">
@@ -1272,22 +1272,22 @@
         <v>6.0</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" ht="40.0" customHeight="true">
@@ -1295,22 +1295,22 @@
         <v>7.0</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H14" s="13" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" ht="40.0" customHeight="true">
@@ -1318,22 +1318,22 @@
         <v>8.0</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" ht="40.0" customHeight="true">
@@ -1341,22 +1341,22 @@
         <v>9.0</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" ht="40.0" customHeight="true">
@@ -1364,22 +1364,22 @@
         <v>10.0</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18" ht="40.0" customHeight="true">
@@ -1387,22 +1387,22 @@
         <v>11.0</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19" ht="40.0" customHeight="true">
@@ -1410,22 +1410,22 @@
         <v>12.0</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" ht="40.0" customHeight="true">
@@ -1433,22 +1433,22 @@
         <v>13.0</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21" ht="40.0" customHeight="true">
@@ -1456,22 +1456,22 @@
         <v>14.0</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="H21" s="13" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
     </row>
     <row r="22" ht="40.0" customHeight="true">
@@ -1479,22 +1479,22 @@
         <v>15.0</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="G22" s="12" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23" ht="40.0" customHeight="true">
@@ -1502,22 +1502,22 @@
         <v>16.0</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" ht="40.0" customHeight="true">
@@ -1525,22 +1525,22 @@
         <v>17.0</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25" ht="40.0" customHeight="true">
@@ -1548,22 +1548,22 @@
         <v>18.0</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H25" s="13" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="26" ht="40.0" customHeight="true">
@@ -1571,19 +1571,19 @@
         <v>19.0</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>109</v>
+        <v>7</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>106</v>
+        <v>7</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>110</v>
+        <v>7</v>
       </c>
       <c r="H26" s="13" t="s">
         <v>7</v>
@@ -1594,19 +1594,19 @@
         <v>20.0</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>113</v>
+        <v>7</v>
       </c>
       <c r="F27" s="15" t="s">
-        <v>114</v>
+        <v>7</v>
       </c>
       <c r="G27" s="15" t="s">
-        <v>115</v>
+        <v>7</v>
       </c>
       <c r="H27" s="16" t="s">
         <v>7</v>
@@ -1640,7 +1640,7 @@
   <sheetData>
     <row r="2" ht="100.0" customHeight="true">
       <c r="B2" s="17" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C2" s="17"/>
       <c r="D2" s="17"/>
@@ -1680,7 +1680,7 @@
       <c r="E5"/>
       <c r="F5"/>
       <c r="G5" s="23" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="H5"/>
     </row>
@@ -1701,7 +1701,7 @@
         <v>6</v>
       </c>
       <c r="D7" s="25" t="s">
-        <v>121</v>
+        <v>5</v>
       </c>
       <c r="E7" s="25" t="s">
         <v>4</v>
@@ -1710,7 +1710,7 @@
         <v>3</v>
       </c>
       <c r="G7" s="25" t="s">
-        <v>2</v>
+        <v>119</v>
       </c>
       <c r="H7" s="26" t="s">
         <v>1</v>
@@ -1724,19 +1724,19 @@
         <v>7</v>
       </c>
       <c r="D8" s="28" t="s">
-        <v>122</v>
+        <v>7</v>
       </c>
       <c r="E8" s="28" t="s">
-        <v>123</v>
+        <v>7</v>
       </c>
       <c r="F8" s="28" t="s">
-        <v>124</v>
+        <v>7</v>
       </c>
       <c r="G8" s="28" t="s">
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="H8" s="29" t="s">
-        <v>13</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9" ht="40.0" customHeight="true">
@@ -1747,19 +1747,19 @@
         <v>7</v>
       </c>
       <c r="D9" s="28" t="s">
-        <v>125</v>
+        <v>7</v>
       </c>
       <c r="E9" s="28" t="s">
-        <v>126</v>
+        <v>7</v>
       </c>
       <c r="F9" s="28" t="s">
-        <v>127</v>
+        <v>7</v>
       </c>
       <c r="G9" s="28" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="H9" s="29" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10" ht="40.0" customHeight="true">
@@ -1767,22 +1767,22 @@
         <v>3.0</v>
       </c>
       <c r="C10" s="28" t="s">
-        <v>130</v>
+        <v>11</v>
       </c>
       <c r="D10" s="28" t="s">
-        <v>131</v>
+        <v>12</v>
       </c>
       <c r="E10" s="28" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="F10" s="28" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="G10" s="28" t="s">
-        <v>134</v>
+        <v>25</v>
       </c>
       <c r="H10" s="29" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11" ht="40.0" customHeight="true">
@@ -1790,22 +1790,22 @@
         <v>4.0</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>16</v>
+        <v>128</v>
       </c>
       <c r="E11" s="28" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="F11" s="28" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="G11" s="28" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="H11" s="29" t="s">
-        <v>140</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" ht="40.0" customHeight="true">
@@ -1813,22 +1813,22 @@
         <v>5.0</v>
       </c>
       <c r="C12" s="28" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="D12" s="28" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="E12" s="28" t="s">
-        <v>23</v>
+        <v>134</v>
       </c>
       <c r="F12" s="28" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="G12" s="28" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="H12" s="29" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13" ht="40.0" customHeight="true">
@@ -1836,22 +1836,22 @@
         <v>6.0</v>
       </c>
       <c r="C13" s="28" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="D13" s="28" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="E13" s="28" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="F13" s="28" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="G13" s="28" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="H13" s="29" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
     </row>
     <row r="14" ht="40.0" customHeight="true">
@@ -1859,22 +1859,22 @@
         <v>7.0</v>
       </c>
       <c r="C14" s="28" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D14" s="28" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="E14" s="28" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="F14" s="28" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="G14" s="28" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="H14" s="29" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15" ht="40.0" customHeight="true">
@@ -1882,22 +1882,22 @@
         <v>8.0</v>
       </c>
       <c r="C15" s="28" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D15" s="28" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="E15" s="28" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="F15" s="28" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="G15" s="28" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="H15" s="29" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
     </row>
     <row r="16" ht="40.0" customHeight="true">
@@ -1905,22 +1905,22 @@
         <v>9.0</v>
       </c>
       <c r="C16" s="28" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D16" s="28" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="E16" s="28" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="F16" s="28" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="G16" s="28" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="H16" s="29" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
     </row>
     <row r="17" ht="40.0" customHeight="true">
@@ -1928,22 +1928,22 @@
         <v>10.0</v>
       </c>
       <c r="C17" s="28" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="D17" s="28" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="E17" s="28" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="F17" s="28" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="G17" s="28" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="H17" s="29" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
     </row>
     <row r="18" ht="40.0" customHeight="true">
@@ -1951,22 +1951,22 @@
         <v>11.0</v>
       </c>
       <c r="C18" s="28" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="D18" s="28" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="E18" s="28" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="F18" s="28" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="G18" s="28" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="H18" s="29" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
     </row>
     <row r="19" ht="40.0" customHeight="true">
@@ -1974,22 +1974,22 @@
         <v>12.0</v>
       </c>
       <c r="C19" s="28" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="D19" s="28" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="E19" s="28" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="F19" s="28" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="G19" s="28" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="H19" s="29" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
     </row>
     <row r="20" ht="40.0" customHeight="true">
@@ -1997,22 +1997,22 @@
         <v>13.0</v>
       </c>
       <c r="C20" s="28" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="D20" s="28" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="E20" s="28" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="F20" s="28" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="G20" s="28" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="H20" s="29" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
     </row>
     <row r="21" ht="40.0" customHeight="true">
@@ -2020,22 +2020,22 @@
         <v>14.0</v>
       </c>
       <c r="C21" s="28" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="D21" s="28" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="E21" s="28" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="F21" s="28" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="G21" s="28" t="s">
-        <v>89</v>
+        <v>187</v>
       </c>
       <c r="H21" s="29" t="s">
-        <v>90</v>
+        <v>188</v>
       </c>
     </row>
     <row r="22" ht="40.0" customHeight="true">
@@ -2043,22 +2043,22 @@
         <v>15.0</v>
       </c>
       <c r="C22" s="28" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="D22" s="28" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="E22" s="28" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="F22" s="28" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="G22" s="28" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="H22" s="29" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
     </row>
     <row r="23" ht="40.0" customHeight="true">
@@ -2066,22 +2066,22 @@
         <v>16.0</v>
       </c>
       <c r="C23" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="D23" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="D23" s="28" t="s">
-        <v>201</v>
-      </c>
       <c r="E23" s="28" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="F23" s="28" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="G23" s="28" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="H23" s="29" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
     </row>
     <row r="24" ht="40.0" customHeight="true">
@@ -2089,22 +2089,22 @@
         <v>17.0</v>
       </c>
       <c r="C24" s="28" t="s">
+        <v>198</v>
+      </c>
+      <c r="D24" s="28" t="s">
         <v>199</v>
       </c>
-      <c r="D24" s="28" t="s">
-        <v>206</v>
-      </c>
       <c r="E24" s="28" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="F24" s="28" t="s">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="G24" s="28" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="H24" s="29" t="s">
-        <v>103</v>
+        <v>203</v>
       </c>
     </row>
     <row r="25" ht="40.0" customHeight="true">
@@ -2112,22 +2112,22 @@
         <v>18.0</v>
       </c>
       <c r="C25" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" s="28" t="s">
         <v>204</v>
       </c>
-      <c r="D25" s="28" t="s">
-        <v>209</v>
-      </c>
       <c r="E25" s="28" t="s">
-        <v>210</v>
+        <v>105</v>
       </c>
       <c r="F25" s="28" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="G25" s="28" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="H25" s="29" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
     </row>
     <row r="26" ht="40.0" customHeight="true">
@@ -2138,16 +2138,16 @@
         <v>208</v>
       </c>
       <c r="D26" s="28" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="E26" s="28" t="s">
-        <v>7</v>
+        <v>210</v>
       </c>
       <c r="F26" s="28" t="s">
-        <v>7</v>
+        <v>207</v>
       </c>
       <c r="G26" s="28" t="s">
-        <v>7</v>
+        <v>211</v>
       </c>
       <c r="H26" s="29" t="s">
         <v>7</v>
@@ -2158,19 +2158,19 @@
         <v>20.0</v>
       </c>
       <c r="C27" s="31" t="s">
+        <v>212</v>
+      </c>
+      <c r="D27" s="31" t="s">
+        <v>213</v>
+      </c>
+      <c r="E27" s="31" t="s">
+        <v>214</v>
+      </c>
+      <c r="F27" s="31" t="s">
         <v>215</v>
       </c>
-      <c r="D27" s="31" t="s">
+      <c r="G27" s="31" t="s">
         <v>216</v>
-      </c>
-      <c r="E27" s="31" t="s">
-        <v>7</v>
-      </c>
-      <c r="F27" s="31" t="s">
-        <v>7</v>
-      </c>
-      <c r="G27" s="31" t="s">
-        <v>7</v>
       </c>
       <c r="H27" s="32" t="s">
         <v>7</v>
